--- a/dotnet-tasks/dotnet-tasks/Resources/input.xlsx
+++ b/dotnet-tasks/dotnet-tasks/Resources/input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_C#\dotnet-tasks\dotnet-tasks\dotnet-tasks\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2A31828-07AC-4626-81B9-2EE204355B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73E049F1-5DBE-45D4-9D3E-01DC4D3091FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1092" yWindow="1512" windowWidth="20988" windowHeight="10068" activeTab="2" xr2:uid="{9BD75906-70E0-4833-A8F9-EC2A38754F4E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{9BD75906-70E0-4833-A8F9-EC2A38754F4E}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
